--- a/docs/IDEA_TRACKER.xlsx
+++ b/docs/IDEA_TRACKER.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
   <si>
     <t>ID</t>
   </si>
@@ -37,6 +37,9 @@
     <t>2026-09-12 06:46</t>
   </si>
   <si>
+    <t>2026-10-07 07:04</t>
+  </si>
+  <si>
     <t>Daily cloud automation (Oracle VM) + local Windows scheduled scan</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>Backlog/ask tracker (this file) -- catch up + maintain going forward</t>
   </si>
   <si>
+    <t>Applied flag the user marks themselves, stored and carried</t>
+  </si>
+  <si>
     <t>jobscout-scan.timer on the shared VM, run_daily.ps1 locally</t>
   </si>
   <si>
@@ -136,6 +142,9 @@
     <t>docs/ASKS.md (pre-existing, Markdown) kept as backup; docs/IDEA_TRACKER.xlsx (new) is primary going forward, per explicit request to keep both</t>
   </si>
   <si>
+    <t>User 2026-10-07: 'create a flag in job search copilot to mark if job is applied from user end or not, user will mark and that need to stored and carried'. Existing today: jobs.status pipeline (new/interested/applied/...), date_applied, mark_applied(), Applied tab. Found while scoping: upsert_job SKIPS known urls so a rescan does NOT clobber marks, BUT sync_from_cloud.py is one-way (cloud-&gt;local) and merge-only (url NOT IN local), so a mark made on either side never reaches the other for a job both already have. Interviewing before building.</t>
+  </si>
+  <si>
     <t>done</t>
   </si>
   <si>
@@ -167,6 +176,9 @@
   </si>
   <si>
     <t>User wants visibility into whether the cloud daily scan is actually running</t>
+  </si>
+  <si>
+    <t>Decisions needed: flag semantics vs existing status; where to mark; whether it must travel laptop&lt;-&gt;cloud; what happens to marked jobs in the lists.</t>
   </si>
 </sst>
 </file>
@@ -524,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -555,16 +567,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -575,16 +587,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -595,13 +607,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -612,13 +624,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -629,16 +641,16 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -649,13 +661,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -666,13 +678,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -683,13 +695,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -700,13 +712,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -717,13 +729,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -734,16 +746,16 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -754,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -774,16 +786,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -794,13 +806,13 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -811,13 +823,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -828,10 +840,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -842,13 +854,13 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -859,10 +871,10 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -873,13 +885,33 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
